--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run4/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run4/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="493">
   <si>
     <t>Filename</t>
   </si>
@@ -808,688 +808,691 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9417,0.0006,0.0243,0.0101</t>
-  </si>
-  <si>
-    <t>0.0035,0.0001,0.0019,0.9980</t>
-  </si>
-  <si>
-    <t>0.9912,0.0001,0.0000,0.0059</t>
-  </si>
-  <si>
-    <t>0.5159,0.0001,0.0001,0.7996</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.9339,0.0015,0.0251,0.0291</t>
+  </si>
+  <si>
+    <t>0.0053,0.0000,0.0004,0.9985</t>
+  </si>
+  <si>
+    <t>0.9902,0.0000,0.0000,0.0081</t>
+  </si>
+  <si>
+    <t>0.4063,0.0001,0.0000,0.8613</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9994,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9972,0.0014,0.0001,0.0003</t>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9957,0.0002,0.0033,0.0000</t>
-  </si>
-  <si>
-    <t>0.0029,0.0003,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.8109,0.0002,0.2983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0518,0.0013,0.9459,0.0010</t>
-  </si>
-  <si>
-    <t>0.9846,0.0012,0.0113,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0080,0.0001</t>
-  </si>
-  <si>
-    <t>0.0044,0.9931,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.9491,0.0030,0.0330,0.0011</t>
-  </si>
-  <si>
-    <t>0.9648,0.0004,0.0392,0.0001</t>
-  </si>
-  <si>
-    <t>0.0543,0.0007,0.9664,0.0001</t>
-  </si>
-  <si>
-    <t>0.0018,0.0008,0.9974,0.0002</t>
-  </si>
-  <si>
-    <t>0.0025,0.0001,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.0001,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.9927,0.0038,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9941,0.0004,0.0037,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0007</t>
-  </si>
-  <si>
-    <t>0.0011,0.9971,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.9946,0.0001,0.0023,0.0004</t>
-  </si>
-  <si>
-    <t>0.9986,0.0002,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.8867,0.1378,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.9978,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0059,0.6432,0.2447,0.0011</t>
-  </si>
-  <si>
-    <t>0.0119,0.0274,0.9294,0.0041</t>
-  </si>
-  <si>
-    <t>0.0011,0.0017,0.9974,0.0002</t>
-  </si>
-  <si>
-    <t>0.2425,0.0001,0.8149,0.0008</t>
-  </si>
-  <si>
-    <t>0.0003,0.0140,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9996,0.0005</t>
-  </si>
-  <si>
-    <t>0.0032,0.3857,0.0007,0.9374</t>
-  </si>
-  <si>
-    <t>0.0004,0.9986,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0009,0.0000</t>
+    <t>0.9979,0.0003,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0062,0.0029,0.9937,0.0003</t>
+  </si>
+  <si>
+    <t>0.2274,0.0001,0.8788,0.0001</t>
+  </si>
+  <si>
+    <t>0.2762,0.0005,0.7964,0.0002</t>
+  </si>
+  <si>
+    <t>0.9949,0.0001,0.0048,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0121,0.9833,0.0061,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.8372,0.0010,0.1601,0.0006</t>
+  </si>
+  <si>
+    <t>0.0278,0.0013,0.9710,0.0007</t>
+  </si>
+  <si>
+    <t>0.0036,0.0002,0.9977,0.0000</t>
+  </si>
+  <si>
+    <t>0.0067,0.0006,0.9929,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.0001,0.9975,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.9794,0.0153,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9773,0.0052,0.0068,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0004</t>
+  </si>
+  <si>
+    <t>0.0576,0.9315,0.0039,0.0001</t>
+  </si>
+  <si>
+    <t>0.7240,0.0016,0.2394,0.0020</t>
+  </si>
+  <si>
+    <t>0.9896,0.0006,0.0047,0.0000</t>
+  </si>
+  <si>
+    <t>0.1511,0.8690,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0025,0.0000</t>
+  </si>
+  <si>
+    <t>0.0306,0.0671,0.7793,0.0006</t>
+  </si>
+  <si>
+    <t>0.0023,0.0001,0.9962,0.0005</t>
+  </si>
+  <si>
+    <t>0.0025,0.0059,0.9951,0.0005</t>
+  </si>
+  <si>
+    <t>0.0147,0.0001,0.9806,0.0009</t>
+  </si>
+  <si>
+    <t>0.0011,0.2548,0.9900,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9996,0.0004</t>
+  </si>
+  <si>
+    <t>0.0009,0.0569,0.0000,0.9861</t>
+  </si>
+  <si>
+    <t>0.0004,0.9989,0.0011,0.0012</t>
+  </si>
+  <si>
+    <t>0.0003,0.9993,0.0033,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0272,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0045,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0003,0.9981,0.0003</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.9990,0.0004</t>
+  </si>
+  <si>
+    <t>0.0042,0.0002,0.9970,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0007,0.9985,0.0009</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9871,0.0124,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9964,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0017,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.1606,0.9876,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.9933,0.9873,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0164,0.9902,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.9991,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.7758,0.0153,0.1172,0.0010</t>
+  </si>
+  <si>
+    <t>0.0003,0.0004,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9982,0.2079,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9902,0.9575,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9948,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0200,0.0002,0.0131,0.9766</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0045,0.0005,0.0002,0.9981</t>
+  </si>
+  <si>
+    <t>0.0034,0.0001,0.0009,0.9979</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0003,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9987,0.9904,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.7001,0.9919,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.0141,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9662,0.9901,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.9929,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9347,0.9759,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0003,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9979,0.0009,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.9960,0.0001,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.9960,0.0067,0.0010</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0700,0.9288,0.0021,0.0009</t>
+  </si>
+  <si>
+    <t>0.8084,0.0034,0.1757,0.0024</t>
+  </si>
+  <si>
+    <t>0.6680,0.0007,0.3958,0.0002</t>
+  </si>
+  <si>
+    <t>0.4215,0.0688,0.2112,0.0012</t>
+  </si>
+  <si>
+    <t>0.3550,0.0081,0.5649,0.0026</t>
+  </si>
+  <si>
+    <t>0.0051,0.0180,0.0003,0.9876</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0014,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0204,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0034,0.0003,0.9956,0.0003</t>
-  </si>
-  <si>
-    <t>0.0009,0.0000,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0010,0.9973,0.0050</t>
-  </si>
-  <si>
-    <t>0.9983,0.0011,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0006,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9962,0.9394,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0110,0.9993,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0018,0.9992,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9888,0.9554,0.0000</t>
+    <t>0.0000,0.9988,0.9802,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9859,0.0075,0.0022,0.0005</t>
+  </si>
+  <si>
+    <t>0.2599,0.7560,0.0071,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9976,0.0002,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0338,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0969,0.9935,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0081,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0007,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.9978,0.0001,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9896,0.0003,0.0083,0.0003</t>
+  </si>
+  <si>
+    <t>0.0699,0.0001,0.9619,0.0003</t>
+  </si>
+  <si>
+    <t>0.9454,0.0052,0.0253,0.0018</t>
+  </si>
+  <si>
+    <t>0.1509,0.0001,0.0001,0.9377</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9986,0.9576,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9975,0.0003,0.0029</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.6285,0.4360,0.0025,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0000,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.1111,0.0000,0.0001,0.9875</t>
+  </si>
+  <si>
+    <t>0.0003,0.0076,0.9987,0.0014</t>
+  </si>
+  <si>
+    <t>0.9979,0.0000,0.0003,0.0016</t>
+  </si>
+  <si>
+    <t>0.9950,0.0001,0.0018,0.0016</t>
+  </si>
+  <si>
+    <t>0.3344,0.7188,0.0027,0.0003</t>
+  </si>
+  <si>
+    <t>0.9853,0.0035,0.0062,0.0009</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.4976,0.4464,0.0076,0.0008</t>
+  </si>
+  <si>
+    <t>0.7926,0.0056,0.1712,0.0048</t>
+  </si>
+  <si>
+    <t>0.9519,0.0106,0.0184,0.0036</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.3899,0.6927,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.8900,0.1480,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.5298,0.5934,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.0103,0.0238,0.9906,0.0008</t>
+  </si>
+  <si>
+    <t>0.9961,0.0045,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9948,0.0011,0.0014,0.0007</t>
+  </si>
+  <si>
+    <t>0.9982,0.0008,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9944,0.0017,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9835,0.0057,0.0062,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0063,0.9986,0.0005</t>
+  </si>
+  <si>
+    <t>0.0010,0.0005,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.1508,0.0072,0.8010,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0018,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0033,0.0000,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0007,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.0611,0.0044,0.9288,0.0020</t>
+  </si>
+  <si>
+    <t>0.0010,0.0007,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.7225,0.0070,0.1767,0.0183</t>
+  </si>
+  <si>
+    <t>0.2215,0.0090,0.7319,0.0012</t>
+  </si>
+  <si>
+    <t>0.1632,0.1181,0.3301,0.0004</t>
+  </si>
+  <si>
+    <t>0.0259,0.0015,0.9754,0.0001</t>
+  </si>
+  <si>
+    <t>0.3050,0.0070,0.6219,0.0039</t>
+  </si>
+  <si>
+    <t>0.1588,0.0202,0.7842,0.0009</t>
+  </si>
+  <si>
+    <t>0.0467,0.9644,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0029,0.9952,0.0069,0.0001</t>
+  </si>
+  <si>
+    <t>0.9120,0.1258,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.8663,0.1501,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0995,0.9001,0.0018,0.0018</t>
+  </si>
+  <si>
+    <t>0.9438,0.0128,0.0135,0.0009</t>
+  </si>
+  <si>
+    <t>0.9972,0.0002,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.9776,0.0013,0.0054,0.0015</t>
+  </si>
+  <si>
+    <t>0.8149,0.0928,0.0121,0.0008</t>
+  </si>
+  <si>
+    <t>0.9666,0.0017,0.0240,0.0005</t>
+  </si>
+  <si>
+    <t>0.0015,0.0005,0.9975,0.0011</t>
+  </si>
+  <si>
+    <t>0.0064,0.0029,0.9853,0.0011</t>
+  </si>
+  <si>
+    <t>0.0031,0.0256,0.9941,0.0002</t>
+  </si>
+  <si>
+    <t>0.0027,0.0030,0.9939,0.0003</t>
+  </si>
+  <si>
+    <t>0.0023,0.0729,0.9757,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9924,0.0050,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.9981,0.0005,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9985,0.0007,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9937,0.0014,0.0015,0.0012</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0005</t>
+  </si>
+  <si>
+    <t>0.0050,0.0890,0.9363,0.0012</t>
+  </si>
+  <si>
+    <t>0.4882,0.0004,0.6364,0.0008</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9995,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0001,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0042,0.9957,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9997,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9398,0.0008,0.0723,0.0005</t>
-  </si>
-  <si>
-    <t>0.9798,0.0030,0.0084,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9940,0.9882,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9879,0.9715,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9870,0.3653,0.0001</t>
-  </si>
-  <si>
-    <t>0.0177,0.0001,0.0255,0.9643</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0006,0.0005,0.0001,0.9996</t>
-  </si>
-  <si>
-    <t>0.0006,0.0003,0.0001,0.9997</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0002,0.9997</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0003,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.8957,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.7864,0.9963,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9961,0.1312,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9593,0.9774,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.9960,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9865,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0005,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0011,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0014,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0023,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0018,0.9992,0.0005</t>
-  </si>
-  <si>
-    <t>0.9986,0.0001,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0037,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9986,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9990,0.0042,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0148,0.9834,0.0018,0.0004</t>
-  </si>
-  <si>
-    <t>0.9237,0.0018,0.0583,0.0029</t>
-  </si>
-  <si>
-    <t>0.0112,0.0005,0.9906,0.0005</t>
-  </si>
-  <si>
-    <t>0.7582,0.0277,0.0894,0.0002</t>
-  </si>
-  <si>
-    <t>0.0255,0.0058,0.9569,0.0025</t>
-  </si>
-  <si>
-    <t>0.0059,0.0018,0.0228,0.9855</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9845,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9881,0.0095,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.5511,0.5081,0.0029,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.7124,0.9951,0.0001</t>
-  </si>
-  <si>
-    <t>0.0023,0.3368,0.8909,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0008,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0056,0.0055,0.9810,0.0005</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9929,0.0003,0.0045,0.0003</t>
-  </si>
-  <si>
-    <t>0.0038,0.0007,0.9952,0.0006</t>
-  </si>
-  <si>
-    <t>0.9046,0.0036,0.0745,0.0026</t>
-  </si>
-  <si>
-    <t>0.1149,0.0000,0.0000,0.9624</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0005,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9887,0.9919,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0327,0.9608,0.0006,0.0018</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.2865,0.7976,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0000,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0131,0.0000,0.0000,0.9989</t>
-  </si>
-  <si>
-    <t>0.0001,0.0063,0.9994,0.0009</t>
-  </si>
-  <si>
-    <t>0.9961,0.0000,0.0005,0.0026</t>
-  </si>
-  <si>
-    <t>0.9990,0.0000,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.3086,0.7209,0.0033,0.0005</t>
-  </si>
-  <si>
-    <t>0.9953,0.0010,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.9977,0.0003,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.3610,0.6073,0.0038,0.0005</t>
-  </si>
-  <si>
-    <t>0.9923,0.0026,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.9809,0.0067,0.0011,0.0012</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9977,0.0005,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9892,0.0133,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1792,0.8516,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.1285,0.9156,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.8415,0.0058,0.1393,0.0008</t>
-  </si>
-  <si>
-    <t>0.9500,0.0634,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9976,0.0013,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9955,0.0014,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9865,0.0049,0.0055,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0259,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.3000,0.0042,0.6751,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0002,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0008,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0455,0.0038,0.9492,0.0021</t>
-  </si>
-  <si>
-    <t>0.0031,0.0006,0.9957,0.0007</t>
-  </si>
-  <si>
-    <t>0.0058,0.0026,0.9909,0.0010</t>
-  </si>
-  <si>
-    <t>0.3981,0.0343,0.2963,0.0004</t>
-  </si>
-  <si>
-    <t>0.2101,0.3524,0.0788,0.0006</t>
-  </si>
-  <si>
-    <t>0.3114,0.0018,0.7159,0.0001</t>
-  </si>
-  <si>
-    <t>0.9855,0.0003,0.0105,0.0006</t>
-  </si>
-  <si>
-    <t>0.4359,0.0271,0.4829,0.0042</t>
-  </si>
-  <si>
-    <t>0.0042,0.9937,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.0038,0.9945,0.0021,0.0002</t>
-  </si>
-  <si>
-    <t>0.9307,0.0823,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9928,0.0060,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.6650,0.3596,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.6234,0.1453,0.0160,0.0053</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.5078,0.0514,0.1877,0.0036</t>
-  </si>
-  <si>
-    <t>0.9739,0.0026,0.0134,0.0006</t>
-  </si>
-  <si>
-    <t>0.0053,0.0006,0.9938,0.0013</t>
-  </si>
-  <si>
-    <t>0.0038,0.0021,0.9925,0.0003</t>
-  </si>
-  <si>
-    <t>0.0348,0.0421,0.9377,0.0008</t>
-  </si>
-  <si>
-    <t>0.2467,0.0029,0.7341,0.0002</t>
-  </si>
-  <si>
-    <t>0.0035,0.0360,0.9902,0.0002</t>
-  </si>
-  <si>
-    <t>0.9966,0.0014,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9923,0.0067,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9986,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9973,0.0005,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0178,0.9082,0.0886,0.0021</t>
-  </si>
-  <si>
-    <t>0.6734,0.0004,0.3887,0.0019</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0028,0.0072,0.9962,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0036,0.0003,0.9964,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.0032,0.9960,0.0005</t>
-  </si>
-  <si>
-    <t>0.9647,0.0002,0.0387,0.0006</t>
-  </si>
-  <si>
-    <t>0.9967,0.0000,0.0038,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0003,0.0000</t>
+    <t>0.0011,0.0113,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0018,0.0002,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.0007,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0025,0.0096,0.9936,0.0038</t>
+  </si>
+  <si>
+    <t>0.9905,0.0002,0.0067,0.0003</t>
+  </si>
+  <si>
+    <t>0.9935,0.0000,0.0095,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0008,0.0002,0.0001</t>
   </si>
   <si>
     <t>0.9996,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9939,0.0015,0.0026,0.0003</t>
-  </si>
-  <si>
-    <t>0.9993,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0100,0.0102,0.9732,0.0001</t>
-  </si>
-  <si>
-    <t>0.0405,0.0003,0.9825,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.0400,0.9787,0.0003</t>
-  </si>
-  <si>
-    <t>0.0038,0.0476,0.9584,0.0016</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0218,0.0037,0.8922,0.0753</t>
-  </si>
-  <si>
-    <t>0.0101,0.0004,0.9872,0.0007</t>
-  </si>
-  <si>
-    <t>0.0998,0.0012,0.8878,0.0019</t>
-  </si>
-  <si>
-    <t>0.2394,0.0000,0.0016,0.9005</t>
-  </si>
-  <si>
-    <t>0.0010,0.0197,0.0001,0.9990</t>
-  </si>
-  <si>
-    <t>0.0060,0.0000,0.0006,0.9983</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.5560,0.0001,0.0011,0.6362</t>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0046,0.0036,0.9893,0.0001</t>
+  </si>
+  <si>
+    <t>0.0176,0.0005,0.9907,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.1865,0.9058,0.0004</t>
+  </si>
+  <si>
+    <t>0.0133,0.0097,0.9561,0.0018</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.4723,0.0001,0.5016,0.0083</t>
+  </si>
+  <si>
+    <t>0.0225,0.0003,0.9722,0.0018</t>
+  </si>
+  <si>
+    <t>0.0066,0.0013,0.9865,0.0023</t>
+  </si>
+  <si>
+    <t>0.6713,0.0000,0.0009,0.6206</t>
+  </si>
+  <si>
+    <t>0.0012,0.0099,0.0001,0.9991</t>
+  </si>
+  <si>
+    <t>0.0134,0.0000,0.0017,0.9949</t>
+  </si>
+  <si>
+    <t>0.8603,0.0004,0.0003,0.2400</t>
   </si>
 </sst>
 </file>
@@ -1875,7 +1878,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1889,7 +1892,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1903,7 +1906,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1917,7 +1920,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1931,7 +1934,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1945,7 +1948,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1959,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1973,7 +1976,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1987,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2001,7 +2004,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2015,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2029,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2043,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2057,7 +2060,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2068,10 +2071,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2085,7 +2088,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2099,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2113,7 +2116,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2127,7 +2130,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2141,7 +2144,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2155,7 +2158,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2169,7 +2172,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2183,7 +2186,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2194,10 +2197,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2211,7 +2214,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2225,7 +2228,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2239,7 +2242,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2253,7 +2256,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2267,7 +2270,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2281,7 +2284,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2295,7 +2298,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2309,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2323,7 +2326,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2337,7 +2340,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2351,7 +2354,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2362,10 +2365,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2379,7 +2382,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2390,10 +2393,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2407,7 +2410,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2421,7 +2424,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2435,7 +2438,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2449,7 +2452,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2463,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2477,7 +2480,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2491,7 +2494,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2505,7 +2508,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2519,7 +2522,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2533,7 +2536,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2547,7 +2550,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2561,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2575,7 +2578,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2589,7 +2592,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2603,7 +2606,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2617,7 +2620,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2631,7 +2634,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2645,7 +2648,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2659,7 +2662,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2673,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2687,7 +2690,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2701,7 +2704,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2715,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2729,7 +2732,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2743,7 +2746,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2757,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2771,7 +2774,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2785,7 +2788,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2799,7 +2802,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2813,7 +2816,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2827,7 +2830,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2841,7 +2844,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2855,7 +2858,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2866,10 +2869,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2883,7 +2886,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2897,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2908,10 +2911,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2925,7 +2928,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2939,7 +2942,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2953,7 +2956,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2967,7 +2970,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2981,7 +2984,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2995,7 +2998,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3009,7 +3012,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3023,7 +3026,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3037,7 +3040,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3051,7 +3054,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3065,7 +3068,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3079,7 +3082,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3093,7 +3096,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3107,7 +3110,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3121,7 +3124,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3135,7 +3138,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3149,7 +3152,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3163,7 +3166,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3177,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3191,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3205,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3219,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>352</v>
+        <v>272</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3233,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3247,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3261,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3275,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>353</v>
+        <v>275</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3289,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3303,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3317,7 +3320,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3331,7 +3334,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3345,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3359,7 +3362,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3373,7 +3376,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3387,7 +3390,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3401,7 +3404,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3415,7 +3418,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3429,7 +3432,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>363</v>
+        <v>306</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3443,7 +3446,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3457,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3471,7 +3474,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3482,10 +3485,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3496,10 +3499,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3513,7 +3516,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3527,7 +3530,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3541,7 +3544,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3555,7 +3558,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>302</v>
+        <v>373</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3569,7 +3572,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3583,7 +3586,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3597,7 +3600,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3611,7 +3614,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3625,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3639,7 +3642,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3653,7 +3656,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>378</v>
+        <v>272</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3667,7 +3670,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>379</v>
+        <v>356</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3695,7 +3698,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>384</v>
@@ -3972,7 +3975,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
         <v>400</v>
@@ -4017,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4115,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D162" t="s">
         <v>409</v>
@@ -4157,7 +4160,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>352</v>
+        <v>412</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4171,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4185,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4199,7 +4202,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>379</v>
+        <v>415</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4213,7 +4216,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4227,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4241,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>352</v>
+        <v>271</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4255,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>352</v>
+        <v>271</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4266,10 +4269,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4280,10 +4283,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4294,10 +4297,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D175" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4308,10 +4311,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4325,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4339,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4353,7 +4356,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4367,7 +4370,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4381,7 +4384,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4395,7 +4398,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4409,7 +4412,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4423,7 +4426,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4437,7 +4440,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4451,7 +4454,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4465,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4479,7 +4482,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4493,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4507,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4521,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4532,10 +4535,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4546,10 +4549,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4560,10 +4563,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D194" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4577,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4588,10 +4591,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4602,10 +4605,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4619,7 +4622,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4633,7 +4636,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4647,7 +4650,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4661,7 +4664,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4672,10 +4675,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4689,7 +4692,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4703,7 +4706,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4717,7 +4720,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4731,7 +4734,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4745,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4759,7 +4762,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4773,7 +4776,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4787,7 +4790,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4801,7 +4804,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4815,7 +4818,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4829,7 +4832,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>352</v>
+        <v>458</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4843,7 +4846,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4857,7 +4860,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4871,7 +4874,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4885,7 +4888,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4899,7 +4902,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4913,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4927,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>462</v>
+        <v>272</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4941,7 +4944,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4952,10 +4955,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4966,10 +4969,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D223" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4983,7 +4986,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>312</v>
+        <v>468</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4997,7 +5000,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5011,7 +5014,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5025,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>468</v>
+        <v>328</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5039,7 +5042,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5053,7 +5056,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>470</v>
+        <v>292</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5067,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5081,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5095,7 +5098,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5109,7 +5112,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5123,7 +5126,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5137,7 +5140,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>346</v>
+        <v>477</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5151,7 +5154,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>476</v>
+        <v>275</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5165,7 +5168,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>354</v>
+        <v>275</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5179,7 +5182,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5193,7 +5196,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5207,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5221,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5235,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>352</v>
+        <v>480</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5249,7 +5252,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5263,7 +5266,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5277,7 +5280,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5291,7 +5294,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5305,7 +5308,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5319,7 +5322,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5333,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5347,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5358,10 +5361,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D251" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5375,7 +5378,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5389,7 +5392,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5403,7 +5406,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>490</v>
+        <v>393</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5428,10 +5431,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
